--- a/templates/import/interaction-timeline.xlsx
+++ b/templates/import/interaction-timeline.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="1" r:id="R5d4dc856e2594bbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="2" r:id="R200fe58d247d4c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="1" r:id="Rf0c6c0992e464b01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="2" r:id="Rc54374d45e7c4fcb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,10 +467,10 @@
         <x:v>channel</x:v>
       </x:c>
       <x:c r="C3" s="8" t="str">
-        <x:v>抖音/天猫/京东</x:v>
+        <x:v>Built-in or custom platform name / 内置或自定义平台名称</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
-        <x:v>抖音</x:v>
+        <x:v>TikTok Shop</x:v>
       </x:c>
       <x:c r="E3" s="8" t="str">
         <x:v>是</x:v>
@@ -884,7 +884,7 @@
         <x:v>SF-DEMO-001</x:v>
       </x:c>
       <x:c r="B2" s="20" t="str">
-        <x:v>抖音</x:v>
+        <x:v>TikTok Shop</x:v>
       </x:c>
       <x:c r="C2" s="20" t="str">
         <x:v>2026-07-01 至 2026-07-07</x:v>
